--- a/artfynd/A 17642-2024 artfynd.xlsx
+++ b/artfynd/A 17642-2024 artfynd.xlsx
@@ -1749,7 +1749,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117753487</v>
+        <v>117753489</v>
       </c>
       <c r="B11" t="n">
         <v>57287</v>
@@ -1789,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>406486</v>
+        <v>406362</v>
       </c>
       <c r="R11" t="n">
-        <v>7063432</v>
+        <v>7063391</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1856,7 +1856,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117753489</v>
+        <v>117753487</v>
       </c>
       <c r="B12" t="n">
         <v>57287</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406362</v>
+        <v>406486</v>
       </c>
       <c r="R12" t="n">
-        <v>7063391</v>
+        <v>7063432</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2070,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117753486</v>
+        <v>117753491</v>
       </c>
       <c r="B14" t="n">
-        <v>57287</v>
+        <v>90510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2082,25 +2082,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1205</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406877</v>
+        <v>406622</v>
       </c>
       <c r="R14" t="n">
-        <v>7063251</v>
+        <v>7063282</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,11 +2146,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre på 3 granar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,7 +2172,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117753485</v>
+        <v>117753488</v>
       </c>
       <c r="B15" t="n">
         <v>57287</v>
@@ -2217,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406863</v>
+        <v>406361</v>
       </c>
       <c r="R15" t="n">
-        <v>7063250</v>
+        <v>7063391</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117753493</v>
+        <v>117753485</v>
       </c>
       <c r="B16" t="n">
-        <v>97753</v>
+        <v>57287</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,25 +2291,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2324,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407000</v>
+        <v>406863</v>
       </c>
       <c r="R16" t="n">
-        <v>7063257</v>
+        <v>7063250</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,6 +2355,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117753488</v>
+        <v>117753492</v>
       </c>
       <c r="B17" t="n">
-        <v>57287</v>
+        <v>90495</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,21 +2402,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406361</v>
+        <v>406544</v>
       </c>
       <c r="R17" t="n">
-        <v>7063391</v>
+        <v>7063469</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,11 +2462,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2493,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117753492</v>
+        <v>117753486</v>
       </c>
       <c r="B18" t="n">
-        <v>90495</v>
+        <v>57287</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,21 +2504,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2533,10 +2528,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406544</v>
+        <v>406877</v>
       </c>
       <c r="R18" t="n">
-        <v>7063469</v>
+        <v>7063251</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,6 +2564,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre på 3 granar</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,10 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117753491</v>
+        <v>117753493</v>
       </c>
       <c r="B19" t="n">
-        <v>90510</v>
+        <v>97753</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2611,21 +2611,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1205</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>406622</v>
+        <v>407000</v>
       </c>
       <c r="R19" t="n">
-        <v>7063282</v>
+        <v>7063257</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 17642-2024 artfynd.xlsx
+++ b/artfynd/A 17642-2024 artfynd.xlsx
@@ -1752,7 +1752,7 @@
         <v>117753489</v>
       </c>
       <c r="B11" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1856,10 +1856,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117753487</v>
+        <v>117753490</v>
       </c>
       <c r="B12" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>406486</v>
+        <v>406976</v>
       </c>
       <c r="R12" t="n">
-        <v>7063432</v>
+        <v>7063203</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på 2 granar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117753490</v>
+        <v>117753486</v>
       </c>
       <c r="B13" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>406976</v>
+        <v>406877</v>
       </c>
       <c r="R13" t="n">
-        <v>7063203</v>
+        <v>7063251</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på 2 granar</t>
+          <t>Ringhack färska och äldre på 3 granar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117753491</v>
+        <v>117753493</v>
       </c>
       <c r="B14" t="n">
-        <v>90510</v>
+        <v>97755</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,21 +2086,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1205</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>406622</v>
+        <v>407000</v>
       </c>
       <c r="R14" t="n">
-        <v>7063282</v>
+        <v>7063257</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117753488</v>
+        <v>117753487</v>
       </c>
       <c r="B15" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>406361</v>
+        <v>406486</v>
       </c>
       <c r="R15" t="n">
-        <v>7063391</v>
+        <v>7063432</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,10 +2279,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117753485</v>
+        <v>117753492</v>
       </c>
       <c r="B16" t="n">
-        <v>57287</v>
+        <v>90497</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2295,21 +2295,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2319,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>406863</v>
+        <v>406544</v>
       </c>
       <c r="R16" t="n">
-        <v>7063250</v>
+        <v>7063469</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,11 +2355,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-06-13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2386,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117753492</v>
+        <v>117753485</v>
       </c>
       <c r="B17" t="n">
-        <v>90495</v>
+        <v>57288</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,21 +2397,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2426,10 +2421,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>406544</v>
+        <v>406863</v>
       </c>
       <c r="R17" t="n">
-        <v>7063469</v>
+        <v>7063250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2462,6 +2457,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2488,10 +2488,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117753486</v>
+        <v>117753488</v>
       </c>
       <c r="B18" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,10 +2528,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>406877</v>
+        <v>406361</v>
       </c>
       <c r="R18" t="n">
-        <v>7063251</v>
+        <v>7063391</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre på 3 granar</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,10 +2595,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117753493</v>
+        <v>117753491</v>
       </c>
       <c r="B19" t="n">
-        <v>97753</v>
+        <v>90512</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2611,21 +2611,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407000</v>
+        <v>406622</v>
       </c>
       <c r="R19" t="n">
-        <v>7063257</v>
+        <v>7063282</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 17642-2024 artfynd.xlsx
+++ b/artfynd/A 17642-2024 artfynd.xlsx
@@ -2697,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118323026</v>
+        <v>118322859</v>
       </c>
       <c r="B20" t="n">
-        <v>78647</v>
+        <v>80140</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,21 +2713,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1249</v>
+        <v>735</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406452</v>
+        <v>406540</v>
       </c>
       <c r="R20" t="n">
-        <v>7063441</v>
+        <v>7063468</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118322859</v>
+        <v>118323026</v>
       </c>
       <c r="B21" t="n">
-        <v>80140</v>
+        <v>78647</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,21 +2815,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>735</v>
+        <v>1249</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406540</v>
+        <v>406452</v>
       </c>
       <c r="R21" t="n">
-        <v>7063468</v>
+        <v>7063441</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 17642-2024 artfynd.xlsx
+++ b/artfynd/A 17642-2024 artfynd.xlsx
@@ -2697,10 +2697,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118322859</v>
+        <v>118323026</v>
       </c>
       <c r="B20" t="n">
-        <v>80140</v>
+        <v>78654</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2713,21 +2713,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>735</v>
+        <v>1249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skuggkraterlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gyalecta friesii</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Flot. ex Körb.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2737,13 +2737,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>406540</v>
+        <v>406452</v>
       </c>
       <c r="R20" t="n">
-        <v>7063468</v>
+        <v>7063441</v>
       </c>
       <c r="S20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118323026</v>
+        <v>118322859</v>
       </c>
       <c r="B21" t="n">
-        <v>78647</v>
+        <v>80147</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2815,21 +2815,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1249</v>
+        <v>735</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skuggkraterlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Gyalecta friesii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Flot. ex Körb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2839,13 +2839,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>406452</v>
+        <v>406540</v>
       </c>
       <c r="R21" t="n">
-        <v>7063441</v>
+        <v>7063468</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
